--- a/eddy_levels.xlsx
+++ b/eddy_levels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katar\OneDrive - nevada.unr.edu\NEON\Abv-Workspace-09202023_laptop\Summarizing-Input-Data\Finalizing Code on 10102023\Site by Site\Monte-Carlo\MC-Matlab-Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katar\Documents\PhD\Chapter 1\Response to Reviewers\Consolidating Final Versions\Public Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF611FB-60BC-42A3-A399-FDD811A8F682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA63022-4DAD-411C-B225-805C92716404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="495" windowWidth="25515" windowHeight="13875" xr2:uid="{EF813E58-B3C2-48AA-8156-D9C00B71ECDE}"/>
+    <workbookView xWindow="960" yWindow="40" windowWidth="18490" windowHeight="15240" xr2:uid="{EF813E58-B3C2-48AA-8156-D9C00B71ECDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,21 +46,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -68,52 +62,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,288 +410,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5AF0510-AFAB-45B1-B2D9-87EC1082A83C}">
   <dimension ref="A1:A56"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.78515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" s="2">
         <v>4</v>
       </c>
     </row>
